--- a/output/roomself_excel/8020.xlsx
+++ b/output/roomself_excel/8020.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>83239</v>
+        <v>198578</v>
       </c>
       <c r="D2" t="n">
-        <v>2336</v>
+        <v>3684</v>
       </c>
       <c r="E2" t="n">
-        <v>366</v>
+        <v>503</v>
       </c>
       <c r="F2" t="n">
-        <v>276</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
@@ -488,17 +488,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>139855</v>
+        <v>203326</v>
       </c>
       <c r="D3" t="n">
-        <v>3008</v>
+        <v>3996</v>
       </c>
       <c r="E3" t="n">
-        <v>415</v>
+        <v>397</v>
       </c>
       <c r="F3" t="n">
         <v>29</v>
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>514986</v>
+        <v>83239</v>
       </c>
       <c r="D4" t="n">
-        <v>9784</v>
+        <v>2336</v>
       </c>
       <c r="E4" t="n">
-        <v>938</v>
+        <v>366</v>
       </c>
       <c r="F4" t="n">
-        <v>642</v>
+        <v>276</v>
       </c>
     </row>
     <row r="5">
@@ -532,17 +532,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22197</v>
+        <v>139855</v>
       </c>
       <c r="D5" t="n">
-        <v>1192</v>
+        <v>3008</v>
       </c>
       <c r="E5" t="n">
-        <v>151</v>
+        <v>415</v>
       </c>
       <c r="F5" t="n">
         <v>29</v>
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>28077</v>
+        <v>107289</v>
       </c>
       <c r="D6" t="n">
-        <v>1352</v>
+        <v>2664</v>
       </c>
       <c r="E6" t="n">
-        <v>191</v>
+        <v>424</v>
       </c>
       <c r="F6" t="n">
-        <v>29</v>
+        <v>302</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>102395</v>
+        <v>104784</v>
       </c>
       <c r="D7" t="n">
-        <v>3240</v>
+        <v>2600</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>354</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>112959</v>
+        <v>19205</v>
       </c>
       <c r="D9" t="n">
-        <v>2880</v>
+        <v>1128</v>
       </c>
       <c r="E9" t="n">
-        <v>521</v>
+        <v>115</v>
       </c>
       <c r="F9" t="n">
-        <v>263</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10">
@@ -642,17 +642,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>19344</v>
+        <v>22197</v>
       </c>
       <c r="D10" t="n">
-        <v>1120</v>
+        <v>1192</v>
       </c>
       <c r="E10" t="n">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="F10" t="n">
         <v>29</v>
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>107289</v>
+        <v>113082</v>
       </c>
       <c r="D11" t="n">
-        <v>2664</v>
+        <v>3204</v>
       </c>
       <c r="E11" t="n">
-        <v>424</v>
+        <v>210</v>
       </c>
       <c r="F11" t="n">
-        <v>302</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>167970</v>
+        <v>26052</v>
       </c>
       <c r="D12" t="n">
-        <v>3356</v>
+        <v>1292</v>
       </c>
       <c r="E12" t="n">
-        <v>525</v>
+        <v>156</v>
       </c>
       <c r="F12" t="n">
-        <v>362</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>104784</v>
+        <v>112959</v>
       </c>
       <c r="D13" t="n">
-        <v>2600</v>
+        <v>2880</v>
       </c>
       <c r="E13" t="n">
-        <v>354</v>
+        <v>521</v>
       </c>
       <c r="F13" t="n">
-        <v>31</v>
+        <v>263</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>26052</v>
+        <v>19344</v>
       </c>
       <c r="D14" t="n">
-        <v>1292</v>
+        <v>1120</v>
       </c>
       <c r="E14" t="n">
-        <v>156</v>
+        <v>124</v>
       </c>
       <c r="F14" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15">
@@ -752,20 +752,64 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>19205</v>
+        <v>167970</v>
       </c>
       <c r="D15" t="n">
-        <v>1128</v>
+        <v>3356</v>
       </c>
       <c r="E15" t="n">
-        <v>115</v>
+        <v>525</v>
       </c>
       <c r="F15" t="n">
-        <v>31</v>
+        <v>362</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>28077</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1352</v>
+      </c>
+      <c r="E16" t="n">
+        <v>191</v>
+      </c>
+      <c r="F16" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>102395</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3240</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/8020.xlsx
+++ b/output/roomself_excel/8020.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,20 @@
       <c r="D2" t="n">
         <v>3684</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>503</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>31</v>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +525,20 @@
       <c r="D3" t="n">
         <v>3996</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>397</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>29</v>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,11 +555,27 @@
       <c r="D4" t="n">
         <v>2336</v>
       </c>
-      <c r="E4" t="n">
-        <v>366</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>276</v>
+        <v>247</v>
+      </c>
+      <c r="G4" t="n">
+        <v>29</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>337</v>
+      </c>
+      <c r="J4" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="5">
@@ -541,12 +593,20 @@
       <c r="D5" t="n">
         <v>3008</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>415</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>29</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,11 +623,27 @@
       <c r="D6" t="n">
         <v>2664</v>
       </c>
-      <c r="E6" t="n">
-        <v>424</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>302</v>
+        <v>393</v>
+      </c>
+      <c r="G6" t="n">
+        <v>29</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>273</v>
+      </c>
+      <c r="J6" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="7">
@@ -585,10 +661,26 @@
       <c r="D7" t="n">
         <v>2600</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>296</v>
+      </c>
+      <c r="G7" t="n">
+        <v>32</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>354</v>
       </c>
-      <c r="F7" t="n">
+      <c r="J7" t="n">
         <v>31</v>
       </c>
     </row>
@@ -607,12 +699,20 @@
       <c r="D8" t="n">
         <v>1528</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="G8" t="n">
+        <v>32</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +729,20 @@
       <c r="D9" t="n">
         <v>1128</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>115</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>31</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +759,20 @@
       <c r="D10" t="n">
         <v>1192</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>151</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>29</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +789,12 @@
       <c r="D11" t="n">
         <v>3204</v>
       </c>
-      <c r="E11" t="n">
-        <v>210</v>
-      </c>
-      <c r="F11" t="n">
-        <v>12</v>
-      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +811,20 @@
       <c r="D12" t="n">
         <v>1292</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>156</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>31</v>
       </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,11 +841,27 @@
       <c r="D13" t="n">
         <v>2880</v>
       </c>
-      <c r="E13" t="n">
-        <v>521</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>263</v>
+        <v>632</v>
+      </c>
+      <c r="G13" t="n">
+        <v>16</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>462</v>
+      </c>
+      <c r="J13" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="14">
@@ -739,12 +879,20 @@
       <c r="D14" t="n">
         <v>1120</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>124</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>29</v>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,11 +909,27 @@
       <c r="D15" t="n">
         <v>3356</v>
       </c>
-      <c r="E15" t="n">
-        <v>525</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>362</v>
+        <v>1018</v>
+      </c>
+      <c r="G15" t="n">
+        <v>16</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>330</v>
+      </c>
+      <c r="J15" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="16">
@@ -783,11 +947,27 @@
       <c r="D16" t="n">
         <v>1352</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
         <v>191</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>29</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>147</v>
+      </c>
+      <c r="J16" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="17">
@@ -805,12 +985,20 @@
       <c r="D17" t="n">
         <v>3240</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="G17" t="n">
+        <v>32</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
